--- a/Data_Processing/frozen/DSI_banking_weights.xlsx
+++ b/Data_Processing/frozen/DSI_banking_weights.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fb93ff5c25ff7e7/Education/University/PhD_UVM/Courses/202526/Fall/CS5870A_DataScienceI/Project/DSE-Project/Data_Processing/frozen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="13_ncr:1_{01B8DCF3-23D5-416A-8C32-4E3468E2A2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AF4B5A0-CA5A-4E67-83F9-3541C7A770C5}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="13_ncr:1_{01B8DCF3-23D5-416A-8C32-4E3468E2A2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{003E09A1-4F03-43FE-9108-6F561170E0C9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{218B1834-7B9F-496F-8C9E-9ADA66E0F810}"/>
   </bookViews>
@@ -738,7 +738,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -772,66 +772,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="13">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="4"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -880,6 +825,60 @@
         <family val="2"/>
         <scheme val="major"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="4"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -975,6 +974,10 @@
 </externalLink>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E5331A8A-DC34-47B0-B054-0A3D27193316}" name="Table1" displayName="Table1" ref="A1:G49" totalsRowShown="0" dataDxfId="12">
   <autoFilter ref="A1:G49" xr:uid="{E5331A8A-DC34-47B0-B054-0A3D27193316}"/>
@@ -985,27 +988,27 @@
     <tableColumn id="1" xr3:uid="{6A60AA0B-559A-4DF8-B4B5-2D5DD271A747}" name="report_type" dataDxfId="11"/>
     <tableColumn id="4" xr3:uid="{28D31664-E05A-4465-84FC-48FC86A2A66B}" name="report_code_partI" dataDxfId="10"/>
     <tableColumn id="7" xr3:uid="{1DA1148A-4DEF-4B5C-ADCC-DC0A24E94E6E}" name="col_name" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{5ABA92C3-CB65-4A42-96AF-DA88BCD5CA1A}" name="assets_line" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{CBAF4344-FA45-44CD-8CD1-1F670106C1B0}" name="report_code_partII" dataDxfId="0">
+    <tableColumn id="2" xr3:uid="{5ABA92C3-CB65-4A42-96AF-DA88BCD5CA1A}" name="assets_line" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{CBAF4344-FA45-44CD-8CD1-1F670106C1B0}" name="report_code_partII" dataDxfId="7">
       <calculatedColumnFormula>SUBSTITUTE(SUBSTITUTE(RIGHT(D2,6),"(",""),")","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{BE84EEA7-9AFE-46CD-A511-713D50D0FDE5}" name="id_bis_min" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{161ACB79-2F49-4925-AF3E-DD16ED25C7F2}" name="id_bis_max" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{BE84EEA7-9AFE-46CD-A511-713D50D0FDE5}" name="id_bis_min" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{161ACB79-2F49-4925-AF3E-DD16ED25C7F2}" name="id_bis_max" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{48B320E7-A662-4A18-B630-CFC166DF034F}" name="Table2" displayName="Table2" ref="A1:E32" totalsRowShown="0" headerRowDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{48B320E7-A662-4A18-B630-CFC166DF034F}" name="Table2" displayName="Table2" ref="A1:E32" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="A1:E32" xr:uid="{48B320E7-A662-4A18-B630-CFC166DF034F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2DE1F72B-A072-4E85-BFC1-0DE3C355DC13}" name="id_bis" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{2DE1F72B-A072-4E85-BFC1-0DE3C355DC13}" name="id_bis" dataDxfId="3">
       <calculatedColumnFormula>IFERROR(A1+1,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F902D440-CEE7-4566-80B5-AEC4B1964B53}" name="Macro_component" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{A6F9D0EF-DB46-40E8-A5CD-A966EAD19261}" name="Risk_associated" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{884DB71E-6E72-462D-B033-EB4B6272D14F}" name="Weight" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{F902D440-CEE7-4566-80B5-AEC4B1964B53}" name="Macro_component" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{A6F9D0EF-DB46-40E8-A5CD-A966EAD19261}" name="Risk_associated" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{884DB71E-6E72-462D-B033-EB4B6272D14F}" name="Weight" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{6772E305-2897-4E20-8D3A-A64046841616}" name="comment"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1374,7 +1377,7 @@
       <c r="D2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="15" t="str">
+      <c r="E2" s="2" t="str">
         <f t="shared" ref="E2:E6" si="0">SUBSTITUTE(SUBSTITUTE(RIGHT(D2,6),"(",""),")","")</f>
         <v>3602</v>
       </c>
@@ -1398,7 +1401,7 @@
       <c r="D3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="15" t="str">
+      <c r="E3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>3604</v>
       </c>
@@ -1422,7 +1425,7 @@
       <c r="D4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="15" t="str">
+      <c r="E4" s="2" t="str">
         <f t="shared" si="0"/>
         <v>3603</v>
       </c>
@@ -1446,7 +1449,7 @@
       <c r="D5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="15" t="str">
+      <c r="E5" s="2" t="str">
         <f t="shared" si="0"/>
         <v>3620</v>
       </c>
@@ -1470,7 +1473,7 @@
       <c r="D6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="15" t="str">
+      <c r="E6" s="2" t="str">
         <f t="shared" si="0"/>
         <v>5993</v>
       </c>
@@ -1494,7 +1497,7 @@
       <c r="D7" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E7" s="15" t="str">
+      <c r="E7" s="2" t="str">
         <f t="shared" ref="E7:E49" si="1">SUBSTITUTE(SUBSTITUTE(RIGHT(D7,6),"(",""),")","")</f>
         <v>0081</v>
       </c>
@@ -1518,7 +1521,7 @@
       <c r="D8" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E8" s="15" t="str">
+      <c r="E8" s="2" t="str">
         <f t="shared" si="1"/>
         <v>0395</v>
       </c>
@@ -1542,7 +1545,7 @@
       <c r="D9" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E9" s="15" t="str">
+      <c r="E9" s="2" t="str">
         <f t="shared" si="1"/>
         <v>0397</v>
       </c>
@@ -1566,7 +1569,7 @@
       <c r="D10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="15" t="str">
+      <c r="E10" s="2" t="str">
         <f t="shared" si="1"/>
         <v>5993</v>
       </c>
@@ -1590,7 +1593,7 @@
       <c r="D11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="15" t="str">
+      <c r="E11" s="2" t="str">
         <f t="shared" si="1"/>
         <v>0010</v>
       </c>
@@ -1614,7 +1617,7 @@
       <c r="D12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="15" t="str">
+      <c r="E12" s="2" t="str">
         <f t="shared" si="1"/>
         <v>1754</v>
       </c>
@@ -1638,7 +1641,7 @@
       <c r="D13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="15" t="str">
+      <c r="E13" s="2" t="str">
         <f t="shared" si="1"/>
         <v>1773</v>
       </c>
@@ -1662,7 +1665,7 @@
       <c r="D14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="15" t="str">
+      <c r="E14" s="2" t="str">
         <f t="shared" si="1"/>
         <v>2130</v>
       </c>
@@ -1686,7 +1689,7 @@
       <c r="D15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="15" t="str">
+      <c r="E15" s="2" t="str">
         <f t="shared" si="1"/>
         <v>2145</v>
       </c>
@@ -1710,7 +1713,7 @@
       <c r="D16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="15" t="str">
+      <c r="E16" s="2" t="str">
         <f t="shared" si="1"/>
         <v>3163</v>
       </c>
@@ -1734,7 +1737,7 @@
       <c r="D17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="15" t="str">
+      <c r="E17" s="2" t="str">
         <f t="shared" si="1"/>
         <v>3164</v>
       </c>
@@ -1758,7 +1761,7 @@
       <c r="D18" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="15" t="str">
+      <c r="E18" s="2" t="str">
         <f t="shared" si="1"/>
         <v>3165</v>
       </c>
@@ -1782,7 +1785,7 @@
       <c r="D19" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="15" t="str">
+      <c r="E19" s="2" t="str">
         <f t="shared" si="1"/>
         <v>2143</v>
       </c>
@@ -1806,7 +1809,7 @@
       <c r="D20" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E20" s="15" t="str">
+      <c r="E20" s="2" t="str">
         <f t="shared" si="1"/>
         <v>3239</v>
       </c>
@@ -1830,7 +1833,7 @@
       <c r="D21" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E21" s="15" t="str">
+      <c r="E21" s="2" t="str">
         <f t="shared" si="1"/>
         <v>3238</v>
       </c>
@@ -1854,7 +1857,7 @@
       <c r="D22" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E22" s="15" t="str">
+      <c r="E22" s="2" t="str">
         <f t="shared" si="1"/>
         <v>3523</v>
       </c>
@@ -1878,7 +1881,7 @@
       <c r="D23" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E23" s="15" t="str">
+      <c r="E23" s="2" t="str">
         <f t="shared" si="1"/>
         <v>0201</v>
       </c>
@@ -1902,7 +1905,7 @@
       <c r="D24" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E24" s="15" t="str">
+      <c r="E24" s="2" t="str">
         <f t="shared" si="1"/>
         <v>0202</v>
       </c>
@@ -1926,7 +1929,7 @@
       <c r="D25" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E25" s="15" t="str">
+      <c r="E25" s="2" t="str">
         <f t="shared" si="1"/>
         <v>0089</v>
       </c>
@@ -1950,7 +1953,7 @@
       <c r="D26" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E26" s="15" t="str">
+      <c r="E26" s="2" t="str">
         <f t="shared" si="1"/>
         <v>0088</v>
       </c>
@@ -1974,7 +1977,7 @@
       <c r="D27" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E27" s="15" t="str">
+      <c r="E27" s="2" t="str">
         <f t="shared" si="1"/>
         <v>0087</v>
       </c>
@@ -1998,7 +2001,7 @@
       <c r="D28" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E28" s="15" t="str">
+      <c r="E28" s="2" t="str">
         <f t="shared" si="1"/>
         <v>3148</v>
       </c>
@@ -2022,7 +2025,7 @@
       <c r="D29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E29" s="15" t="str">
+      <c r="E29" s="2" t="str">
         <f t="shared" si="1"/>
         <v>2145</v>
       </c>
@@ -2046,7 +2049,7 @@
       <c r="D30" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E30" s="15" t="str">
+      <c r="E30" s="2" t="str">
         <f t="shared" si="1"/>
         <v>2150</v>
       </c>
@@ -2070,7 +2073,7 @@
       <c r="D31" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E31" s="15" t="str">
+      <c r="E31" s="2" t="str">
         <f t="shared" si="1"/>
         <v>0365</v>
       </c>
@@ -2094,7 +2097,7 @@
       <c r="D32" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="15" t="str">
+      <c r="E32" s="2" t="str">
         <f t="shared" si="1"/>
         <v>2125</v>
       </c>
@@ -2118,7 +2121,7 @@
       <c r="D33" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E33" s="15" t="str">
+      <c r="E33" s="2" t="str">
         <f t="shared" si="1"/>
         <v>2723</v>
       </c>
@@ -2142,7 +2145,7 @@
       <c r="D34" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E34" s="15" t="str">
+      <c r="E34" s="2" t="str">
         <f t="shared" si="1"/>
         <v>2160</v>
       </c>
@@ -2166,7 +2169,7 @@
       <c r="D35" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E35" s="15" t="str">
+      <c r="E35" s="2" t="str">
         <f t="shared" si="1"/>
         <v>2160</v>
       </c>
@@ -2190,7 +2193,7 @@
       <c r="D36" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="15" t="str">
+      <c r="E36" s="2" t="str">
         <f t="shared" si="1"/>
         <v>0027</v>
       </c>
@@ -2214,7 +2217,7 @@
       <c r="D37" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E37" s="15" t="str">
+      <c r="E37" s="2" t="str">
         <f t="shared" si="1"/>
         <v>3545</v>
       </c>
@@ -2238,7 +2241,7 @@
       <c r="D38" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E38" s="15" t="str">
+      <c r="E38" s="2" t="str">
         <f t="shared" si="1"/>
         <v>3656</v>
       </c>
@@ -2262,7 +2265,7 @@
       <c r="D39" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E39" s="15" t="str">
+      <c r="E39" s="2" t="str">
         <f t="shared" si="1"/>
         <v>0390</v>
       </c>
@@ -2286,7 +2289,7 @@
       <c r="D40" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E40" s="15" t="str">
+      <c r="E40" s="2" t="str">
         <f t="shared" si="1"/>
         <v>5369</v>
       </c>
@@ -2310,7 +2313,7 @@
       <c r="D41" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="15" t="str">
+      <c r="E41" s="2" t="str">
         <f t="shared" si="1"/>
         <v>B529</v>
       </c>
@@ -2334,7 +2337,7 @@
       <c r="D42" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E42" s="15" t="str">
+      <c r="E42" s="2" t="str">
         <f t="shared" si="1"/>
         <v>B987</v>
       </c>
@@ -2358,7 +2361,7 @@
       <c r="D43" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E43" s="15" t="str">
+      <c r="E43" s="2" t="str">
         <f t="shared" si="1"/>
         <v>B989</v>
       </c>
@@ -2382,7 +2385,7 @@
       <c r="D44" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E44" s="15" t="str">
+      <c r="E44" s="2" t="str">
         <f t="shared" si="1"/>
         <v>1299</v>
       </c>
@@ -2406,7 +2409,7 @@
       <c r="D45" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E45" s="15" t="str">
+      <c r="E45" s="2" t="str">
         <f t="shared" si="1"/>
         <v>0277</v>
       </c>
@@ -2430,7 +2433,7 @@
       <c r="D46" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E46" s="15" t="str">
+      <c r="E46" s="2" t="str">
         <f t="shared" si="1"/>
         <v>6791</v>
       </c>
@@ -2454,7 +2457,7 @@
       <c r="D47" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E47" s="15" t="str">
+      <c r="E47" s="2" t="str">
         <f t="shared" si="1"/>
         <v>0400</v>
       </c>
@@ -2478,7 +2481,7 @@
       <c r="D48" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E48" s="15" t="str">
+      <c r="E48" s="2" t="str">
         <f t="shared" si="1"/>
         <v>2170</v>
       </c>
@@ -2498,7 +2501,7 @@
       <c r="D49" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E49" s="15" t="str">
+      <c r="E49" s="2" t="str">
         <f t="shared" si="1"/>
         <v>JA22</v>
       </c>
@@ -2636,8 +2639,9 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
